--- a/results/job_matches_2026-06-02.xlsx
+++ b/results/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>KLS Martin Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, GCP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cb8e3e7f036669</t>
+          <t>https://www.indeed.com/viewjob?jk=7b464e799ea8089d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Block Labs</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malta, MT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, BigQuery, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8521c97662c0b57</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cb8e3e7f036669</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Block Labs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Malta, MT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727aba117da7b7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a8521c97662c0b57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
+          <t>https://www.indeed.com/viewjob?jk=727aba117da7b7a0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mid-Level Business Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd8003ebc53d5ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Mid-Level Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Justhire Technology</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
+          <t>https://www.indeed.com/viewjob?jk=bd8003ebc53d5ab3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SmartTIX</t>
+          <t>Justhire Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
+          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps &amp; Platform Engineer (AWS / CI/CD)</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>SmartTIX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d70a9322c9786b</t>
+          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
+          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
+          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
+          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
+          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
+          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Senior Solution Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4a9a916464c719</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c563ff6c6c61af</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4a9a916464c719</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcaf6daec0d7c9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c563ff6c6c61af</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data &amp; AI Intern</t>
+          <t>ERP Data Management Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70e856c1968e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=dcaf6daec0d7c9d8</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SkySlope</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
+          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Security / PCI and Compliance</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Edlio LLC</t>
+          <t>SkySlope</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324d5a4d0e21543e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>NLM QA Specialist I - III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Fervo Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
+          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Oracle, MongoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8ec8d04972fc0b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
+          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
+          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Instructional Assistant (Cloud Systems Engineering)</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Per Scholas</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27337ed48c446924</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02afe5b9fb166a85</t>
+          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BusPatrol</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63d448fe3a8c008</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f1133accccfb0f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP Platform Services &amp; Frameworks</t>
+          <t>Senior DevOps Engineer/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Stellar Cyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29f217984e78bba</t>
+          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Agiloft</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
+          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d9272c185c23e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580e242948a318a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c35a8039f2d699</t>
+          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Data Architect Snowflake Medallion Architecture</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4cb44123f0e681</t>
+          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AL/ML Engineer / Azure Policy, AWS SCP</t>
+          <t>Databricks Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3a5d8cf56d01694</t>
+          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
+          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
+          <t>https://www.indeed.com/viewjob?jk=3d9272c185c23e1a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Brotherhood Mutual Insurance Company</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
+          <t>https://www.indeed.com/viewjob?jk=580e242948a318a3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2162,11 +2162,11 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c35a8039f2d699</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,15 +2193,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4cb44123f0e681</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
+          <t>https://www.indeed.com/viewjob?jk=0731089eba8c8af5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, AI Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
+          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
+          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
+          <t>Engineer I- Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chrome Hearts</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hollywood, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Brotherhood Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
+          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
+          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineer</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e77849a606bd380</t>
+          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe31b446b710556</t>
+          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Application Integration Engineer</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2fa8b6f031cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3430d97e76b325</t>
+          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist - Retail</t>
+          <t>NLM Security Specialist I - III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Splunk, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,164 +2701,164 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
+          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
+          <t>Chrome Hearts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=924a8a8705d9e686</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Sr. Software Engineer, AI Specialist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cd611e4010c8c8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
+          <t>Salma Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d9430066096f6a2</t>
+          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SDN Automation Engineer</t>
+          <t>deviceWISE UI Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e809e3665c70de7d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b48387ff7308a3c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior Data Automation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Wikimedia Foundation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
+          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer-WO-003</t>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd5f96e1434ab45</t>
+          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior GTM Data Engineer</t>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, ELT, dbt, Power BI, Tableau, Python, SQL</t>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a48857d65986eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – ClickHouse Infrastructure</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,532 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09956aa680bb5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cloud &amp; DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>First Orion</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Enterprise Data Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e77849a606bd380</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MuleSoft QA Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbe31b446b710556</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer -Ford Pro Intelligence</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MuleSoft Developer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a3430d97e76b325</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist - Retail</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LoadUp Technologies</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4a9537487871ae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ketch</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DevOps Engineer-WO-003</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SOSi</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecd5f96e1434ab45</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior GTM Data Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Global Payments</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, ELT, dbt, Power BI, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73a48857d65986eb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-02.xlsx
+++ b/results/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SmartTIX</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
+          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0719f5d865d28c</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>SmartTIX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, HDFS, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2623aa90a431c062</t>
+          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, RDS, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5b7f70487a08c4</t>
+          <t>https://www.indeed.com/viewjob?jk=2623aa90a431c062</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8263a31ade65f67d</t>
+          <t>https://www.indeed.com/viewjob?jk=db0719f5d865d28c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
+          <t>AWS, Glue, Lambda, ECS, RDS, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5b7f70487a08c4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8263a31ade65f67d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
+          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
+          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
+          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
+          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
+          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4a9a916464c719</t>
+          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Observability</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c563ff6c6c61af</t>
+          <t>https://www.indeed.com/viewjob?jk=04cf0c668327fad5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect</t>
+          <t>Senior Solution Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcaf6daec0d7c9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Java</t>
+          <t>ERP Data Management Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Knott Cleaning</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a5aeeb93f9ed7b</t>
+          <t>https://www.indeed.com/viewjob?jk=dcaf6daec0d7c9d8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RWD Delivery Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Cloud Storage, Scala, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480648c59cb92063</t>
+          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4a9a916464c719</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SkySlope</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c563ff6c6c61af</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NLM QA Specialist I - III</t>
+          <t>Full Stack Software Engineer - Java</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Knott Cleaning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a5aeeb93f9ed7b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fervo Energy</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
+          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>RWD Delivery Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Oracle, MongoDB, Splunk, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Cloud Storage, Scala, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8ec8d04972fc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=480648c59cb92063</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>NLM QA Specialist I - III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Oracle, MongoDB, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
+          <t>https://www.indeed.com/viewjob?jk=7d8ec8d04972fc0b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Fervo Energy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>SkySlope</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>William Blair &amp; Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
+          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
+          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BusPatrol</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f1133accccfb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer/Site Reliability Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stellar Cyber</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
+          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Agiloft</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
+          <t>https://www.indeed.com/viewjob?jk=5afa70752c2ff290</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,94 +1931,94 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
+          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect - Enterprise AI &amp; Generative AI Platforms - Multiple locations; Remote</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
+          <t>https://www.indeed.com/viewjob?jk=77b44ab330bb3208</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect Snowflake Medallion Architecture</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>BusPatrol</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f1133accccfb0f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Databricks Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Stellar Cyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
+          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Agiloft</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d9272c185c23e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580e242948a318a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c35a8039f2d699</t>
+          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4cb44123f0e681</t>
+          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect Snowflake Medallion Architecture</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
+          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Databricks Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0731089eba8c8af5</t>
+          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=3d9272c185c23e1a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer I- Software</t>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
+          <t>https://www.indeed.com/viewjob?jk=580e242948a318a3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c35a8039f2d699</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Brotherhood Mutual Insurance Company</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4cb44123f0e681</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
+          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
+          <t>https://www.indeed.com/viewjob?jk=0731089eba8c8af5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
+          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
+          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NLM Security Specialist I - III</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Splunk, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
+          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chrome Hearts</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hollywood, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, AI Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
+          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
+          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Salma Health</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
+          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>deviceWISE UI Developer</t>
+          <t>Engineer I- Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
+          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b48387ff7308a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Automation Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Brotherhood Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
+          <t>NLM Security Specialist I - III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Wikimedia Foundation</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Splunk, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
+          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Chrome Hearts</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
+          <t>Sr. Software Engineer, AI Specialist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Salma Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>deviceWISE UI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineer</t>
+          <t>Senior Data Automation Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e77849a606bd380</t>
+          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer -Ford Pro Intelligence</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3430d97e76b325</t>
+          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist - Retail</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
+          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b48387ff7308a3c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LoadUp Technologies</t>
+          <t>Wikimedia Foundation</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a9537487871ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ketch</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
+          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer-WO-003</t>
+          <t>Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd5f96e1434ab45</t>
+          <t>https://www.indeed.com/viewjob?jk=4e77849a606bd380</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Developer</t>
+          <t>Senior Software Engineer -Ford Pro Intelligence</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
+          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior GTM Data Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,402 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a3430d97e76b325</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist - Retail</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Material Bank</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ketch</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DevOps Engineer-WO-003</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SOSi</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecd5f96e1434ab45</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>S3, ECS, Azure, Scala, SQL Server, MySQL, CI/CD, Azure DevOps, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fde32c0099d09aeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior GTM Data Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Global Payments</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>RDS, BigQuery, Scala, Snowflake, ELT, dbt, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=73a48857d65986eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-02.xlsx
+++ b/results/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Block Labs</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malta, MT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, BigQuery, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8521c97662c0b57</t>
+          <t>https://www.indeed.com/viewjob?jk=727aba117da7b7a0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727aba117da7b7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
+          <t>https://www.indeed.com/viewjob?jk=a6033e89c4de2fb1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mid-Level Business Intelligence Analyst</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Justhire Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd8003ebc53d5ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Justhire Technology</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
+          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Emmes Company, LLC</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>SmartTIX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
+          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SmartTIX</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
+          <t>https://www.indeed.com/viewjob?jk=db0719f5d865d28c</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0719f5d865d28c</t>
+          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bar Harbor, ME, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, RDS, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5b7f70487a08c4</t>
+          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8263a31ade65f67d</t>
+          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
+          <t>Informatica Product Owner - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>The Jackson Laboratory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Farmington, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
+          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>Alachua, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
+          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
+          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Solution Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>James Avery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
+          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
+          <t>https://www.indeed.com/viewjob?jk=35c6213ec2315d39</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Observability</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04cf0c668327fad5</t>
+          <t>https://www.indeed.com/viewjob?jk=885c41578e07ffb5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
+          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Full Stack Software Engineer - Java</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Knott Cleaning</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,29 +1291,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a5aeeb93f9ed7b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>RWD Delivery Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Cloud Storage, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,54 +1336,54 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4a9a916464c719</t>
+          <t>https://www.indeed.com/viewjob?jk=480648c59cb92063</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c563ff6c6c61af</t>
+          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Java</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Knott Cleaning</t>
+          <t>SkySlope</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a5aeeb93f9ed7b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>NLM QA Specialist I - III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RWD Delivery Architect</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Fervo Energy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Cloud Storage, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480648c59cb92063</t>
+          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NLM QA Specialist I - III</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
+          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Oracle, MongoDB, Splunk, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d8ec8d04972fc0b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fervo Energy</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
+          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SkySlope</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
+          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c04b4f9272c367</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
+          <t>https://www.indeed.com/viewjob?jk=5afa70752c2ff290</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>AI Architect - Enterprise AI &amp; Generative AI Platforms - Multiple locations; Remote</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
+          <t>https://www.indeed.com/viewjob?jk=77b44ab330bb3208</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9be0e32027026424</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afa70752c2ff290</t>
+          <t>https://www.indeed.com/viewjob?jk=e68993f91fa3f1b4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
+          <t>https://www.indeed.com/viewjob?jk=628201dada39104f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
+          <t>https://www.indeed.com/viewjob?jk=17ee918f557dad60</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Architect - Enterprise AI &amp; Generative AI Platforms - Multiple locations; Remote</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b44ab330bb3208</t>
+          <t>https://www.indeed.com/viewjob?jk=d89f724d90d39f1a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BusPatrol</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f1133accccfb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb73281d17dd7f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer/Site Reliability Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stellar Cyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,207 +2036,207 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
+          <t>https://www.indeed.com/viewjob?jk=928d83034a8588c4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
+          <t>https://www.indeed.com/viewjob?jk=e19e44b8ef2cbfc7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Agiloft</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
+          <t>https://www.indeed.com/viewjob?jk=bd91d3d4221ab6c8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
+          <t>https://www.indeed.com/viewjob?jk=709cd6837bc31b47</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
+          <t>https://www.indeed.com/viewjob?jk=cf62483ea94871fc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ad3b9ffbf1a1c5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect Snowflake Medallion Architecture</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,942 +2246,942 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
+          <t>https://www.indeed.com/viewjob?jk=27464971a8de0b62</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Databricks Site Reliability Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
+          <t>https://www.indeed.com/viewjob?jk=ac11b38d058e456a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
+          <t>https://www.indeed.com/viewjob?jk=1c427842476a9845</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d9272c185c23e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e590e631ed3731a1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580e242948a318a3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9680315af02331</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c35a8039f2d699</t>
+          <t>https://www.indeed.com/viewjob?jk=770c38ee65bb6062</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4cb44123f0e681</t>
+          <t>https://www.indeed.com/viewjob?jk=6a328d7361f15199</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
+          <t>https://www.indeed.com/viewjob?jk=9e159100e52ecbaf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0731089eba8c8af5</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f8b67ac923201</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
+          <t>https://www.indeed.com/viewjob?jk=c55ec597154d2272</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb331ccb94124f99</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
+          <t>https://www.indeed.com/viewjob?jk=a2cec2ae3282a2e6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4fcd73d5c5e6202f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
+          <t>https://www.indeed.com/viewjob?jk=586c88459fbb0f45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+          <t>https://www.indeed.com/viewjob?jk=e48010dc3a1202d3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2337d6b23ef3e27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=ced6f7a33f86e685</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer I- Software</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
+          <t>https://www.indeed.com/viewjob?jk=18f275e19ded062a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8708de56a7f54bb9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Brotherhood Mutual Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
+          <t>https://www.indeed.com/viewjob?jk=3959e4229ad7ab7b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NLM Security Specialist I - III</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Splunk, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
+          <t>https://www.indeed.com/viewjob?jk=144e16ada1b5a9ae</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chrome Hearts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hollywood, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=8571d804c3e2af21</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, AI Specialist</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
+          <t>https://www.indeed.com/viewjob?jk=15445b689370c772</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Salma Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e63010208c6e8b0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>deviceWISE UI Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ecfc2a85326ce</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Automation Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=70bd54ff64ef9514</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe31b446b710556</t>
+          <t>https://www.indeed.com/viewjob?jk=5f22be107213655b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c3954b773cda740</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
+          <t>https://www.indeed.com/viewjob?jk=7520782451b1ea33</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,369 +3261,369 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
+          <t>https://www.indeed.com/viewjob?jk=8a16389d2443deac</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b48387ff7308a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff8f530a20b3705d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wikimedia Foundation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=42d5bf7d1da35b7e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fbcbf5c35629fe8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
+          <t>https://www.indeed.com/viewjob?jk=4ec57015b662f733</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=b0e4be7e924b1ce2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
+          <t>https://www.indeed.com/viewjob?jk=3117cbef0400ac1d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e77849a606bd380</t>
+          <t>https://www.indeed.com/viewjob?jk=75220828d5bebb59</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer -Ford Pro Intelligence</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=57688f9ac8e58277</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3430d97e76b325</t>
+          <t>https://www.indeed.com/viewjob?jk=2fff3ba0293d267a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist - Retail</t>
+          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, IAM, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
+          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
+          <t>Senior DevOps Engineer/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Stellar Cyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3632,46 +3632,46 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
+          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a125832a9faf2b6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>Agiloft</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4639de61892c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Material Bank</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf0998b173a8e22</t>
+          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ketch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
+          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DevOps Engineer-WO-003</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd5f96e1434ab45</t>
+          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Data Architect Snowflake Medallion Architecture</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>S3, ECS, Azure, Scala, SQL Server, MySQL, CI/CD, Azure DevOps, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde32c0099d09aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior GTM Data Engineer</t>
+          <t>Databricks Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, ELT, dbt, Power BI, Tableau, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a48857d65986eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,40 +3926,4205 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Bass Pro Shops</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Exostar</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EMERY SAPP &amp; SONS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Engineer I- Software</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Brotherhood Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Arlington Heights, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Williamsville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Salma Health</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, AI Specialist</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>NLM Security Specialist I - III</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Lexical Intelligence, LLC</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Splunk, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>deviceWISE UI Developer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Chrome Hearts</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Hollywood, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Palm Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Senior Azure DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>IT Labs</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Senior AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Scorpion</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Senior AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Scorpion</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Senior AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Scorpion</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b48387ff7308a3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Senior Data Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Wikimedia Foundation</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Ziosk</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Ziosk</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Solutions Engineer(Python/Airflow)</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>EDB</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Cloud &amp; DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>First Orion</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>North Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Enterprise Data Engineer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Shelter Insurance</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e77849a606bd380</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>MuleSoft QA Engineer</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbe31b446b710556</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=853f304c4fea8ef7</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=855d996d6f780ae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0dfce6c1d4ad55a</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=777bd37e520ab857</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76da643450ea8ff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=367f57f5d7c46512</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70958ae9c65a14af</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ca4d042a90c3371</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34833a6b6b34b0bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8a3699e30c2caf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2694b298c133118</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31a495d44eb4372b</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist - Retail</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer -Ford Pro Intelligence</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Ketch</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>DevOps Engineer-WO-003</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SOSi</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecd5f96e1434ab45</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>S3, ECS, Azure, Scala, SQL Server, MySQL, CI/CD, Azure DevOps, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fde32c0099d09aeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Senior GTM Data Engineer</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Global Payments</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, ELT, dbt, Power BI, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73a48857d65986eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
           <t>Senior Data Solutions Developer</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Commerce</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D219" t="n">
         <v>10.4</v>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
         </is>

--- a/results/job_matches_2026-06-02.xlsx
+++ b/results/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G220"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cb8e3e7f036669</t>
+          <t>https://www.indeed.com/viewjob?jk=a6033e89c4de2fb1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Hadoop</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727aba117da7b7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud &amp; AI Platform Architect (contract)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
+          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Justhire Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6033e89c4de2fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>AWS Full Stack Developer W Amazon Kinesis &amp; AWS Connect - Remote Role</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Justhire Technology</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lawrenceville, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, SQS, API Gateway, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
+          <t>https://www.indeed.com/viewjob?jk=e182003963ce0897</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SmartTIX</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, HDFS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65fe6b467bcebd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2623aa90a431c062</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0719f5d865d28c</t>
+          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Solution Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, HDFS, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2623aa90a431c062</t>
+          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
+          <t>ERP Data Management Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,172 +881,172 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
+          <t>https://www.indeed.com/viewjob?jk=dcaf6daec0d7c9d8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bar Harbor, ME, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db23110a8baa26ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22eadc10f98f86e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>James Avery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Farmington, CT, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc73b585f3756066</t>
+          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alachua, FL, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031cba0efbfb272c</t>
+          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Informatica Product Owner - Remote</t>
+          <t>Full Stack Software Engineer - Java</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Jackson Laboratory</t>
+          <t>Knott Cleaning</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,89 +1056,89 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356fb2d131354301</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a5aeeb93f9ed7b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
+          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>James Avery</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>RWD Delivery Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,116 +1147,116 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Cloud Storage, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c6213ec2315d39</t>
+          <t>https://www.indeed.com/viewjob?jk=480648c59cb92063</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>NLM QA Specialist I - III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885c41578e07ffb5</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Fervo Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcaf6daec0d7c9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Java</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Knott Cleaning</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a5aeeb93f9ed7b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RWD Delivery Architect</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Cloud Storage, Scala, ETL</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480648c59cb92063</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SkySlope</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,137 +1406,137 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3139e590b6a0719</t>
+          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NLM QA Specialist I - III</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
+          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fervo Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
+          <t>AWS, IAM, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
+          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Agiloft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Blob Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b20eb19409e2893</t>
+          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,172 +1581,172 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Java Developer (Secret)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc2ced04d49bd7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
+          <t>https://www.indeed.com/viewjob?jk=494dfe5922212ee2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Data Architect Snowflake Medallion Architecture</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Databricks Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afa70752c2ff290</t>
+          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Architect - Enterprise AI &amp; Generative AI Platforms - Multiple locations; Remote</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b44ab330bb3208</t>
+          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bass Pro Shops</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be0e32027026424</t>
+          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior DevOps Engineer/Site Reliability Engineer-East Coast</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stellar Cyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e68993f91fa3f1b4</t>
+          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Analytics Software Engineer IV</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,242 +1896,242 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628201dada39104f</t>
+          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17ee918f557dad60</t>
+          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89f724d90d39f1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb73281d17dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928d83034a8588c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19e44b8ef2cbfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd91d3d4221ab6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709cd6837bc31b47</t>
+          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf62483ea94871fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,294 +2211,294 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ad3b9ffbf1a1c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27464971a8de0b62</t>
+          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Engineer I- Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac11b38d058e456a</t>
+          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c427842476a9845</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Brotherhood Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e590e631ed3731a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Engineer, Digital Products</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NDWA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9680315af02331</t>
+          <t>https://www.indeed.com/viewjob?jk=807809781a081dc7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Sr. Software Engineer, AI Specialist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=770c38ee65bb6062</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Salma Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a328d7361f15199</t>
+          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>NLM Security Specialist I - III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Splunk, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e159100e52ecbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,15 +2508,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f8b67ac923201</t>
+          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,15 +2543,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55ec597154d2272</t>
+          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,15 +2578,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb331ccb94124f99</t>
+          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,15 +2613,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2cec2ae3282a2e6</t>
+          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,15 +2648,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fcd73d5c5e6202f</t>
+          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,15 +2683,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586c88459fbb0f45</t>
+          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,15 +2718,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48010dc3a1202d3</t>
+          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,15 +2753,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2337d6b23ef3e27</t>
+          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,15 +2788,15 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced6f7a33f86e685</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,15 +2823,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f275e19ded062a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,15 +2858,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8708de56a7f54bb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,15 +2893,15 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3959e4229ad7ab7b</t>
+          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,15 +2928,15 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=144e16ada1b5a9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,15 +2963,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8571d804c3e2af21</t>
+          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,15 +2998,15 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15445b689370c772</t>
+          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,15 +3033,15 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e63010208c6e8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,15 +3068,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ecfc2a85326ce</t>
+          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,15 +3103,15 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70bd54ff64ef9514</t>
+          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,15 +3138,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f22be107213655b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,15 +3173,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3954b773cda740</t>
+          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,15 +3208,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7520782451b1ea33</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,15 +3243,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a16389d2443deac</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,15 +3278,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff8f530a20b3705d</t>
+          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,15 +3313,15 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42d5bf7d1da35b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,15 +3348,15 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fbcbf5c35629fe8</t>
+          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,15 +3383,15 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ec57015b662f733</t>
+          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,15 +3418,15 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e4be7e924b1ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,15 +3453,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3117cbef0400ac1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,15 +3488,15 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75220828d5bebb59</t>
+          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,15 +3523,15 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57688f9ac8e58277</t>
+          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,15 +3558,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fff3ba0293d267a</t>
+          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
+          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer/Site Reliability Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Stellar Cyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,207 +3646,207 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
+          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Agiloft</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60d1f21a4e182da</t>
+          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d74fea61e0c268af</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Architect Snowflake Medallion Architecture</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,129 +3856,129 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
+          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Databricks Site Reliability Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
+          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
+          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>Chrome Hearts</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,24 +3986,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>deviceWISE UI Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Automation Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Engineer I- Software</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,124 +4101,124 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe31b446b710556</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
+          <t>https://www.indeed.com/viewjob?jk=26e873e4dbdd44d8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Brotherhood Mutual Insurance Company</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
+          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4227,186 +4227,186 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
+          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
+          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
+          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
+          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
+          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
+          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
+          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
+          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
+          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
+          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
+          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
+          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
+          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
+          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
+          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,154 +5186,154 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wikimedia Foundation</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
+          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
+          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Full-Stack Data BI Engineer (on-site)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
+          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
+          <t>https://www.indeed.com/viewjob?jk=4e77849a606bd380</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,15 +5343,15 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
+          <t>https://www.indeed.com/viewjob?jk=853f304c4fea8ef7</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Data Engineer (Azure Focus)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Blue Ridge Care</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,2737 +5396,287 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Lakebase Sales Specialist - Retail</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Data Solutions Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Data Solutions Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
+          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior GTM Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, BigQuery, Scala, Snowflake, ELT, dbt, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
+          <t>https://www.indeed.com/viewjob?jk=73a48857d65986eb</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Software Engineer -Ford Pro Intelligence</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
+          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ketch</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
+          <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>DevOps Engineer-WO-003</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SOSi</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Salma Health</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, AI Specialist</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>NLM Security Specialist I - III</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Lexical Intelligence, LLC</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Splunk, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>deviceWISE UI Developer</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Chrome Hearts</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Hollywood, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Palm Beach, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Scorpion</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Scorpion</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Scorpion</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>AMH</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Draper, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b48387ff7308a3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Senior Data Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Wikimedia Foundation</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Ziosk</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Ziosk</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>EDB</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdbfaeb882fcaf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Cloud &amp; DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>First Orion</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>North Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, RDS, Databricks, Spark, CI/CD, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53bbcc678b9b2126</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Enterprise Data Engineer</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Shelter Insurance</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Columbia, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e77849a606bd380</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe31b446b710556</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=853f304c4fea8ef7</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=855d996d6f780ae7</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0dfce6c1d4ad55a</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=777bd37e520ab857</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76da643450ea8ff1</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=367f57f5d7c46512</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70958ae9c65a14af</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ca4d042a90c3371</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34833a6b6b34b0bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a3699e30c2caf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2694b298c133118</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31a495d44eb4372b</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist - Retail</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer -Ford Pro Intelligence</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Ketch</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>DevOps Engineer-WO-003</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>SOSi</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ecd5f96e1434ab45</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>.NET Developer</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>S3, ECS, Azure, Scala, SQL Server, MySQL, CI/CD, Azure DevOps, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fde32c0099d09aeb</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Dave</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Senior GTM Data Engineer</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Global Payments</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Scala, Snowflake, ELT, dbt, Power BI, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73a48857d65986eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Senior Data Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Commerce</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Senior Data Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Commerce</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-02.xlsx
+++ b/results/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>Senior Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6033e89c4de2fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=d846903d81c33e82</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
+          <t>https://www.indeed.com/viewjob?jk=a6033e89c4de2fb1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Platform Architect (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,29 +591,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
+          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>Cloud &amp; AI Platform Architect (contract)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Justhire Technology</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,38 +622,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
+          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Full Stack Developer W Amazon Kinesis &amp; AWS Connect - Remote Role</t>
+          <t>DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Justhire Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lawrenceville, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, SQS, API Gateway, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e182003963ce0897</t>
+          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>AWS Full Stack Developer W Amazon Kinesis &amp; AWS Connect - Remote Role</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Emmes Company, LLC</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Lawrenceville, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, SQS, API Gateway, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e182003963ce0897</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,52 +731,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
+          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, HDFS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2623aa90a431c062</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer</t>
+          <t>Full Stack and AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,29 +836,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5ca6c0823ba9179</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f94b5acff92730</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,38 +867,38 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcaf6daec0d7c9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d05047e3838d26d9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ERP Data Management Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
+          <t>https://www.indeed.com/viewjob?jk=dcaf6daec0d7c9d8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
+          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>James Avery</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
+          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Java</t>
+          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Knott Cleaning</t>
+          <t>James Avery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,104 +1046,104 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a5aeeb93f9ed7b</t>
+          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RWD Delivery Architect</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Cloud Storage, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480648c59cb92063</t>
+          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NLM QA Specialist I - III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Direct Travel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf4356318d88930</t>
+          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fervo Energy</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34260a70256866e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Fervo Energy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a382e3d5a9c0a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7e9e84a12c3534</t>
+          <t>https://www.indeed.com/viewjob?jk=25b51410dd8ffd88</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75befce9107331c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fed518d6fe919b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14cc48e7f7f837c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
+          <t>https://www.indeed.com/viewjob?jk=c48d396577280e6f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
+          <t>Informatics Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
+          <t>https://www.indeed.com/viewjob?jk=8c1e23f8adfafe11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
+          <t>https://www.indeed.com/viewjob?jk=0f8a17e02da010e4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agiloft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, IAM, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
+          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Data Layer Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>SOSi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, S3, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2564466ca73964ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e045fbd4ef10a7c1</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Java Developer (Secret)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Agiloft</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc2ced04d49bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494dfe5922212ee2</t>
+          <t>https://www.indeed.com/viewjob?jk=d05d8b56b72079c9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Architect Snowflake Medallion Architecture</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
+          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Databricks Site Reliability Engineer</t>
+          <t>Java Developer (Secret)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc2ced04d49bd7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
+          <t>https://www.indeed.com/viewjob?jk=494dfe5922212ee2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect Snowflake Medallion Architecture</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bass Pro Shops</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150c1c460a8f2243</t>
+          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer/Site Reliability Engineer-East Coast</t>
+          <t>Databricks Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Stellar Cyber</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,104 +1851,104 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
+          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Software Engineer IV</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
+          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
+          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer/Site Reliability Engineer-East Coast</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Stellar Cyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
+          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Analytics Software Engineer IV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255f7cfbea2f42a</t>
+          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d42f664c1bc212</t>
+          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Fashion Nova</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Beverly Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b23576df86210e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=b80f5d754f1ffd13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=268739eff36de340</t>
+          <t>https://www.indeed.com/viewjob?jk=de8841e4e75fbe68</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55697a169692173b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ca03311ac42217</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
+          <t>https://www.indeed.com/viewjob?jk=b9faea0d55a841c9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=2abbc5f73ae2028d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
+          <t>https://www.indeed.com/viewjob?jk=33de66454718a7f8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
+          <t>https://www.indeed.com/viewjob?jk=f96d64f561456df6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer I- Software</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
+          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, ELT, dbt, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ec0556f52ecfdf</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Brotherhood Mutual Insurance Company</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae07d8ce5e9b6c72</t>
+          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Engineer, Digital Products</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NDWA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807809781a081dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, AI Specialist</t>
+          <t>Engineer I- Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, PostgreSQL, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a0b45e1676a63</t>
+          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Salma Health</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a585d9e5f8d2b5e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NLM Security Specialist I - III</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Nabis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Splunk, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c516f232221676d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e75782fef7c9f07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Snowflake, Time Travel, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e01343345f387b3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
+          <t>https://www.indeed.com/viewjob?jk=745e80023e3ea1c3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Engineer, Digital Products</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NDWA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
+          <t>https://www.indeed.com/viewjob?jk=807809781a081dc7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Salma Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
+          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
+          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
+          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
+          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
+          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
+          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
+          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
+          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
+          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
+          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
+          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
+          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
+          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
+          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
+          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
+          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
+          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
+          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
+          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
+          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
+          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
+          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Retail Technology &amp; Platform Engineering</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Chrome Hearts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hollywood, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd17c64ea657ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>deviceWISE UI Developer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,139 +4021,139 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Automation Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe31b446b710556</t>
+          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>deviceWISE UI Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26e873e4dbdd44d8</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Data Automation Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
+          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Palm Beach, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
+          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
+          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
+          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
+          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
+          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
+          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
+          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
+          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
+          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
+          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
+          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
+          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
+          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
+          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Wikimedia Foundation</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d0f91e0077746c</t>
+          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Full-Stack Data BI Engineer (on-site)</t>
+          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Wikimedia Foundation</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, BigQuery, Spark, Snowflake, Dimensional Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd42e61b1f00ae70</t>
+          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
         </is>
       </c>
     </row>
@@ -5333,17 +5333,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Finance Analytics &amp; AI Senior Consultant</t>
+          <t>.Net Fullstack Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Oracle, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853f304c4fea8ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=0d011c6ed693c14f</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure Focus)</t>
+          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Blue Ridge Care</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
+          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist - Retail</t>
+          <t>Data System Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa83c7a2449f337</t>
+          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Developer</t>
+          <t>Data Engineer (Azure Focus)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Blue Ridge Care</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Developer</t>
+          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
+          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
+          <t>Senior Data Solutions Developer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
+          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior GTM Data Engineer</t>
+          <t>Senior Data Solutions Developer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, ELT, dbt, Power BI, Tableau, Python, SQL</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a48857d65986eb</t>
+          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
         </is>
       </c>
     </row>
@@ -5642,41 +5642,6 @@
       <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>DevOps Engineer-WO-003</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>SOSi</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd5f96e1434ab45</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-02.xlsx
+++ b/results/job_matches_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud &amp; AI Platform Architect (contract)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0f811fcc1e86b90</t>
+          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Platform Architect (contract)</t>
+          <t>AWS Full Stack Developer W Amazon Kinesis &amp; AWS Connect - Remote Role</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lawrenceville, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, SQS, API Gateway, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
+          <t>https://www.indeed.com/viewjob?jk=e182003963ce0897</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Cloud Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Justhire Technology</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,164 +671,164 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde27c3a7c822c19</t>
+          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Full Stack Developer W Amazon Kinesis &amp; AWS Connect - Remote Role</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Capstone Logistics, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lawrenceville, GA, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, SQS, API Gateway, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e182003963ce0897</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Engineer I, DevOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Emmes Company, LLC</t>
+          <t>CareMetx, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f343c9a6ac4261</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
+          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
+          <t>Full Stack and AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f94b5acff92730</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack and AI Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f94b5acff92730</t>
+          <t>https://www.indeed.com/viewjob?jk=d05047e3838d26d9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05047e3838d26d9</t>
+          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ERP Data Management Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcaf6daec0d7c9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - API Platform Engineer - CDH</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>James Avery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
+          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
+          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>James Avery</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior AI Software Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Pyramid Systems Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
+          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
+          <t>https://www.indeed.com/viewjob?jk=324835225383dd25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pyramid Systems Inc</t>
+          <t>Direct Travel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88814833d520dd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Direct Travel</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Konexus, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, SQS, ECS, IAM, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6951570b4be5bb92</t>
+          <t>https://www.indeed.com/viewjob?jk=01891cd9bc4d364f</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE</t>
+          <t>Informatics Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Steerbridge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48d396577280e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c1e23f8adfafe11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Informatics Architect</t>
+          <t>Senior Full Stack JS Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, Fact Tables, Dimension Tables</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c1e23f8adfafe11</t>
+          <t>https://www.indeed.com/viewjob?jk=ff84a48bf7f2b214</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Senior Full Stack JS Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f8a17e02da010e4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a341fbae4ab3a40</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
+          <t>Senior Full Stack JS Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
+          <t>https://www.indeed.com/viewjob?jk=2d370271ca54d590</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Layer Engineer</t>
+          <t>Senior Full Stack JS Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,84 +1581,84 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e045fbd4ef10a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=8dc0480a620e54b0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack JS Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8f514248ec1f9f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Agiloft</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
+          <t>https://www.indeed.com/viewjob?jk=c48d396577280e6f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,15 +1668,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05d8b56b72079c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f8a17e02da010e4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
+          <t>https://www.indeed.com/viewjob?jk=2907e0725b12b84d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Developer (Secret)</t>
+          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfc2ced04d49bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Spark, Scala, Kafka, Talend, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494dfe5922212ee2</t>
+          <t>https://www.indeed.com/viewjob?jk=09530a3bb367b138</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect Snowflake Medallion Architecture</t>
+          <t>Data Layer Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>SOSi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, S3, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
+          <t>https://www.indeed.com/viewjob?jk=e045fbd4ef10a7c1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Databricks Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
+          <t>https://www.indeed.com/viewjob?jk=2ca45297ce13a403</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Agiloft</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, IAM, RDS, Spark, Scala, Snowflake, DynamoDB, MLflow</t>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, DynamoDB, Data Modeling, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47245914b1e5195</t>
+          <t>https://www.indeed.com/viewjob?jk=d337c4cad6629101</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer/Site Reliability Engineer-East Coast</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stellar Cyber</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
+          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Software Engineer IV</t>
+          <t>Java Developer (Secret)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
+          <t>https://www.indeed.com/viewjob?jk=6dfc2ced04d49bd7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
+          <t>https://www.indeed.com/viewjob?jk=494dfe5922212ee2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect Snowflake Medallion Architecture</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fashion Nova</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80f5d754f1ffd13</t>
+          <t>https://www.indeed.com/viewjob?jk=c25d688094faa093</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, CI/CD, Terraform, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8841e4e75fbe68</t>
+          <t>https://www.indeed.com/viewjob?jk=c694a4bd3cc1f564</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer/Site Reliability Engineer-East Coast</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Stellar Cyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ca03311ac42217</t>
+          <t>https://www.indeed.com/viewjob?jk=294d519c166048b0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Software Engineer IV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9faea0d55a841c9</t>
+          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abbc5f73ae2028d</t>
+          <t>https://www.indeed.com/viewjob?jk=b344a99057758897</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fashion Nova</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Beverly Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33de66454718a7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b80f5d754f1ffd13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96d64f561456df6</t>
+          <t>https://www.indeed.com/viewjob?jk=de8841e4e75fbe68</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ca03311ac42217</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9faea0d55a841c9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
+          <t>https://www.indeed.com/viewjob?jk=2abbc5f73ae2028d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
+          <t>https://www.indeed.com/viewjob?jk=33de66454718a7f8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer I- Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Data Modeling, ELT, dbt</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503dad30dd16cac7</t>
+          <t>https://www.indeed.com/viewjob?jk=f96d64f561456df6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a585d9e5f8d2b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nabis</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e75782fef7c9f07</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Snowflake, Time Travel, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e01343345f387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>Redshift, Google Cloud Platform, BigQuery, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745e80023e3ea1c3</t>
+          <t>https://www.indeed.com/viewjob?jk=313ba908abc9de9c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer, Digital Products</t>
+          <t>Senior Cloud Technical Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NDWA</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Cloud Storage, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807809781a081dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc613361b67cb34</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Salma Health</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Snowflake, Time Travel, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e01343345f387b3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
+          <t>https://www.indeed.com/viewjob?jk=745e80023e3ea1c3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
+          <t>https://www.indeed.com/viewjob?jk=4a585d9e5f8d2b5e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nabis</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
+          <t>https://www.indeed.com/viewjob?jk=7e75782fef7c9f07</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Salma Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Medallion Architecture, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=63a4deb064ceb6b1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Engineer, Digital Products</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NDWA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
+          <t>https://www.indeed.com/viewjob?jk=807809781a081dc7</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
+          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
+          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
+          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
+          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
+          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
+          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
+          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
+          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
+          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
+          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
+          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
+          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
+          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
+          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
+          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
+          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
+          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
+          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
+          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
+          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>deviceWISE UI Developer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,77 +4126,77 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Automation Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,59 +4276,59 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>deviceWISE UI Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
+          <t>https://www.indeed.com/viewjob?jk=538c5daa04e61b19</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Data Automation Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
+          <t>https://www.indeed.com/viewjob?jk=b688e7ede93fd9cc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Palm Beach, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
+          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
+          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
+          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
+          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
+          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
+          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
+          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
+          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
+          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
+          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
+          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
+          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
+          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
+          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
+          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Wikimedia Enterprise New</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Wikimedia Foundation</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dbb3c218f7e9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e77849a606bd380</t>
+          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>.Net Fullstack Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d011c6ed693c14f</t>
+          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
+          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data System Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Franciscan Health</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure Focus)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Blue Ridge Care</t>
+          <t>Scorpion</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Winchester, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
+          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
+          <t>.Net Fullstack Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d011c6ed693c14f</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Developer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Developer</t>
+          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
+          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer -Ford Pro Intelligence</t>
+          <t>Data System Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Data Engineer (Azure Focus)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ketch</t>
+          <t>Blue Ridge Care</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,15 +5631,225 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Data Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer -Ford Pro Intelligence</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48384f9bd2f18aa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ketch</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=710a102d3715faa8</t>
         </is>
